--- a/outputs/42902.xlsx
+++ b/outputs/42902.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="3">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -104,8 +104,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -302,170 +306,191 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>2</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,1)</f>
+        <v>name</v>
+      </c>
+      <c r="E1" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,2)</f>
+        <v>address</v>
+      </c>
+      <c r="F1" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,3)</f>
+        <v>city st zip</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>2</v>
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,4)</f>
+        <v>name</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,5)</f>
+        <v>address</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,6)</f>
+        <v>city st zip</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,7)</f>
+        <v>name</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,8)</f>
+        <v>address</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,9)</f>
+        <v>city st zip</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>2</v>
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,10)</f>
+        <v>name</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,11)</f>
+        <v>address</v>
+      </c>
+      <c r="F4" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,12)</f>
+        <v>city st zip</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>2</v>
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,13)</f>
+        <v>name</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,14)</f>
+        <v>address</v>
+      </c>
+      <c r="F5" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,15)</f>
+        <v>city st zip</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>2</v>
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,16)</f>
+        <v>name</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,17)</f>
+        <v>address</v>
+      </c>
+      <c r="F6" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,18)</f>
+        <v>city st zip</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>2</v>
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,19)</f>
+        <v>name</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,20)</f>
+        <v>address</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f aca="false">INDEX($A$1:$A$21,21)</f>
+        <v>city st zip</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>2</v>
       </c>
     </row>

--- a/outputs/42902.xlsx
+++ b/outputs/42902.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="3">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -309,119 +309,98 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,1)</f>
-        <v>name</v>
-      </c>
-      <c r="E1" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,2)</f>
-        <v>address</v>
-      </c>
-      <c r="F1" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,3)</f>
-        <v>city st zip</v>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,4)</f>
-        <v>name</v>
-      </c>
-      <c r="E2" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,5)</f>
-        <v>address</v>
-      </c>
-      <c r="F2" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,6)</f>
-        <v>city st zip</v>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,7)</f>
-        <v>name</v>
-      </c>
-      <c r="E3" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,8)</f>
-        <v>address</v>
-      </c>
-      <c r="F3" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,9)</f>
-        <v>city st zip</v>
+      <c r="D3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,10)</f>
-        <v>name</v>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,11)</f>
-        <v>address</v>
-      </c>
-      <c r="F4" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,12)</f>
-        <v>city st zip</v>
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,13)</f>
-        <v>name</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,14)</f>
-        <v>address</v>
-      </c>
-      <c r="F5" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,15)</f>
-        <v>city st zip</v>
+      <c r="D5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,16)</f>
-        <v>name</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,17)</f>
-        <v>address</v>
-      </c>
-      <c r="F6" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,18)</f>
-        <v>city st zip</v>
+      <c r="D6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,19)</f>
-        <v>name</v>
-      </c>
-      <c r="E7" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,20)</f>
-        <v>address</v>
-      </c>
-      <c r="F7" s="1" t="str">
-        <f aca="false">INDEX($A$1:$A$21,21)</f>
-        <v>city st zip</v>
+      <c r="D7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
